--- a/public/plantilla-cantidades-unificado.xlsx
+++ b/public/plantilla-cantidades-unificado.xlsx
@@ -10022,32 +10022,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>18300</colOff>
-      <row>6</row>
-      <rowOff>80025</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1404000"/>
@@ -10059,11 +10059,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-cantidades-unificado.xlsx
+++ b/public/plantilla-cantidades-unificado.xlsx
@@ -10254,7 +10254,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="638" min="1" max="1"/>
-    <col width="16" customWidth="1" style="565" min="2" max="2"/>
+    <col width="25.8" customWidth="1" style="565" min="2" max="2"/>
     <col width="30.77734375" customWidth="1" style="565" min="3" max="3"/>
     <col width="20.77734375" customWidth="1" style="565" min="4" max="4"/>
     <col width="12.77734375" customWidth="1" style="638" min="5" max="5"/>
